--- a/data/time_order.xlsx
+++ b/data/time_order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\章超涵\Desktop\sim-degree2.0 - 副本\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\章超涵\Desktop\sim-degree2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBBED33-43AC-4D20-9436-A4D69824DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA102BF3-C085-4ED6-9308-B9C8E4F914B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="915" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="915" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carbon Peak (Overall)" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,26 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="251">
   <si>
+    <t>地方</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时序</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>中央</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -962,26 +982,6 @@
   <si>
     <t>广西省完善广西能源绿色低碳转型体制机制和政策措施的实施方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>local</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>document</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>time</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>timeorder</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>note</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1048,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1065,11 +1065,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1369,27 +1375,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4">
         <v>44493</v>
@@ -1401,10 +1407,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4">
         <v>44721</v>
@@ -1416,10 +1422,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
         <v>44731</v>
@@ -1431,10 +1437,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4">
         <v>44735</v>
@@ -1446,10 +1452,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4">
         <v>44750</v>
@@ -1461,10 +1467,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4">
         <v>44750</v>
@@ -1476,10 +1482,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4">
         <v>44764</v>
@@ -1491,10 +1497,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4">
         <v>44764</v>
@@ -1506,10 +1512,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4">
         <v>44782</v>
@@ -1521,10 +1527,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C11" s="4">
         <v>44784</v>
@@ -1536,10 +1542,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C12" s="4">
         <v>44798</v>
@@ -1551,10 +1557,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4">
         <v>44816</v>
@@ -1566,10 +1572,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C14" s="4">
         <v>44827</v>
@@ -1581,10 +1587,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C15" s="4">
         <v>44834</v>
@@ -1596,10 +1602,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4">
         <v>44836</v>
@@ -1611,10 +1617,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4">
         <v>44845</v>
@@ -1626,10 +1632,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C18" s="4">
         <v>44862</v>
@@ -1641,10 +1647,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C19" s="4">
         <v>44869</v>
@@ -1656,10 +1662,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="4">
         <v>44883</v>
@@ -1671,10 +1677,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4">
         <v>44913</v>
@@ -1686,10 +1692,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C22" s="4">
         <v>44913</v>
@@ -1701,10 +1707,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C23" s="4">
         <v>44924</v>
@@ -1716,10 +1722,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C24" s="4">
         <v>44926</v>
@@ -1731,10 +1737,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C25" s="4">
         <v>44931</v>
@@ -1746,10 +1752,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C26" s="4">
         <v>44963</v>
@@ -1779,29 +1785,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C2" s="7">
+        <v>209</v>
+      </c>
+      <c r="C2" s="8">
         <v>44867</v>
       </c>
       <c r="D2" s="5">
@@ -1811,12 +1817,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="7">
+        <v>210</v>
+      </c>
+      <c r="C3" s="8">
         <v>44921</v>
       </c>
       <c r="D3" s="5">
@@ -1826,12 +1832,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="7">
+        <v>211</v>
+      </c>
+      <c r="C4" s="8">
         <v>44925</v>
       </c>
       <c r="D4" s="5">
@@ -1841,12 +1847,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="7">
+        <v>212</v>
+      </c>
+      <c r="C5" s="8">
         <v>45090</v>
       </c>
       <c r="D5" s="5">
@@ -1856,12 +1862,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="7">
+        <v>213</v>
+      </c>
+      <c r="C6" s="8">
         <v>45135</v>
       </c>
       <c r="D6" s="5">
@@ -1871,12 +1877,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="7">
+        <v>214</v>
+      </c>
+      <c r="C7" s="8">
         <v>45146</v>
       </c>
       <c r="D7" s="5">
@@ -1886,12 +1892,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="7">
+        <v>215</v>
+      </c>
+      <c r="C8" s="8">
         <v>45274</v>
       </c>
       <c r="D8" s="5">
@@ -1901,12 +1907,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C9" s="7">
+        <v>216</v>
+      </c>
+      <c r="C9" s="8">
         <v>45316</v>
       </c>
       <c r="D9" s="5">
@@ -1916,12 +1922,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C10" s="7">
+        <v>217</v>
+      </c>
+      <c r="C10" s="8">
         <v>45321</v>
       </c>
       <c r="D10" s="5">
@@ -1931,12 +1937,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="7">
+        <v>218</v>
+      </c>
+      <c r="C11" s="8">
         <v>45342</v>
       </c>
       <c r="D11" s="5">
@@ -1946,12 +1952,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12" s="7">
+        <v>219</v>
+      </c>
+      <c r="C12" s="8">
         <v>45364</v>
       </c>
       <c r="D12" s="5">
@@ -1961,12 +1967,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13" s="7">
+        <v>220</v>
+      </c>
+      <c r="C13" s="8">
         <v>45400</v>
       </c>
       <c r="D13" s="5">
@@ -1994,29 +2000,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="7">
+        <v>221</v>
+      </c>
+      <c r="C2" s="8">
         <v>44852</v>
       </c>
       <c r="D2" s="5">
@@ -2026,12 +2032,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" s="7">
+        <v>222</v>
+      </c>
+      <c r="C3" s="8">
         <v>44963</v>
       </c>
       <c r="D3" s="5">
@@ -2041,12 +2047,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="7">
+        <v>223</v>
+      </c>
+      <c r="C4" s="8">
         <v>44971</v>
       </c>
       <c r="D4" s="5">
@@ -2056,12 +2062,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="7">
+        <v>224</v>
+      </c>
+      <c r="C5" s="8">
         <v>44971</v>
       </c>
       <c r="D5" s="5">
@@ -2071,12 +2077,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="7">
+        <v>225</v>
+      </c>
+      <c r="C6" s="8">
         <v>44977</v>
       </c>
       <c r="D6" s="5">
@@ -2086,12 +2092,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="7">
+        <v>226</v>
+      </c>
+      <c r="C7" s="8">
         <v>45022</v>
       </c>
       <c r="D7" s="5">
@@ -2101,12 +2107,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="7">
+        <v>227</v>
+      </c>
+      <c r="C8" s="8">
         <v>45043</v>
       </c>
       <c r="D8" s="5">
@@ -2116,12 +2122,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="7">
+        <v>228</v>
+      </c>
+      <c r="C9" s="8">
         <v>45169</v>
       </c>
       <c r="D9" s="5">
@@ -2131,12 +2137,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="7">
+        <v>229</v>
+      </c>
+      <c r="C10" s="8">
         <v>45176</v>
       </c>
       <c r="D10" s="5">
@@ -2164,29 +2170,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C2" s="7">
+        <v>230</v>
+      </c>
+      <c r="C2" s="8">
         <v>44706</v>
       </c>
       <c r="D2" s="5">
@@ -2196,12 +2202,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="7">
+        <v>231</v>
+      </c>
+      <c r="C3" s="8">
         <v>44725</v>
       </c>
       <c r="D3" s="5">
@@ -2211,12 +2217,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" s="7">
+        <v>232</v>
+      </c>
+      <c r="C4" s="8">
         <v>44835</v>
       </c>
       <c r="D4" s="5">
@@ -2226,12 +2232,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="7">
+        <v>233</v>
+      </c>
+      <c r="C5" s="8">
         <v>44865</v>
       </c>
       <c r="D5" s="5">
@@ -2241,12 +2247,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="7">
+        <v>234</v>
+      </c>
+      <c r="C6" s="8">
         <v>44903</v>
       </c>
       <c r="D6" s="5">
@@ -2256,12 +2262,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="7">
+        <v>235</v>
+      </c>
+      <c r="C7" s="8">
         <v>44910</v>
       </c>
       <c r="D7" s="5">
@@ -2271,12 +2277,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C8" s="7">
+        <v>236</v>
+      </c>
+      <c r="C8" s="8">
         <v>44911</v>
       </c>
       <c r="D8" s="5">
@@ -2286,12 +2292,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" s="7">
+        <v>237</v>
+      </c>
+      <c r="C9" s="8">
         <v>44918</v>
       </c>
       <c r="D9" s="5">
@@ -2301,12 +2307,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="7">
+        <v>238</v>
+      </c>
+      <c r="C10" s="8">
         <v>44955</v>
       </c>
       <c r="D10" s="5">
@@ -2316,12 +2322,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="7">
+        <v>239</v>
+      </c>
+      <c r="C11" s="8">
         <v>44957</v>
       </c>
       <c r="D11" s="5">
@@ -2331,12 +2337,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="7">
+        <v>240</v>
+      </c>
+      <c r="C12" s="8">
         <v>44963</v>
       </c>
       <c r="D12" s="5">
@@ -2346,12 +2352,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="7">
+        <v>241</v>
+      </c>
+      <c r="C13" s="8">
         <v>44967</v>
       </c>
       <c r="D13" s="5">
@@ -2361,12 +2367,12 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="7">
+        <v>242</v>
+      </c>
+      <c r="C14" s="8">
         <v>45009</v>
       </c>
       <c r="D14" s="5">
@@ -2376,12 +2382,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" s="7">
+        <v>243</v>
+      </c>
+      <c r="C15" s="8">
         <v>45020</v>
       </c>
       <c r="D15" s="5">
@@ -2391,12 +2397,12 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" s="7">
+        <v>244</v>
+      </c>
+      <c r="C16" s="8">
         <v>45037</v>
       </c>
       <c r="D16" s="5">
@@ -2406,12 +2412,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="7">
+        <v>245</v>
+      </c>
+      <c r="C17" s="8">
         <v>45112</v>
       </c>
       <c r="D17" s="5">
@@ -2421,12 +2427,12 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="7">
+        <v>246</v>
+      </c>
+      <c r="C18" s="8">
         <v>45126</v>
       </c>
       <c r="D18" s="5">
@@ -2436,12 +2442,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="7">
+        <v>247</v>
+      </c>
+      <c r="C19" s="8">
         <v>45264</v>
       </c>
       <c r="D19" s="5">
@@ -2451,13 +2457,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="D20" s="5">
         <v>19</v>
@@ -2485,27 +2491,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>50</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C2" s="4">
         <v>44461</v>
@@ -2517,10 +2523,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>51</v>
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C3" s="4">
         <v>44530</v>
@@ -2532,10 +2538,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="C4" s="4">
         <v>44566</v>
@@ -2547,10 +2553,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="C5" s="4">
         <v>44569</v>
@@ -2562,10 +2568,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>54</v>
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="C6" s="4">
         <v>44576</v>
@@ -2577,10 +2583,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C7" s="4">
         <v>44609</v>
@@ -2592,10 +2598,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="C8" s="4">
         <v>44633</v>
@@ -2607,10 +2613,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C9" s="4">
         <v>44633</v>
@@ -2622,10 +2628,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C10" s="4">
         <v>44634</v>
@@ -2637,10 +2643,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>60</v>
+        <v>15</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C11" s="4">
         <v>44657</v>
@@ -2652,10 +2658,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="C12" s="4">
         <v>44668</v>
@@ -2667,10 +2673,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>62</v>
+        <v>47</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C13" s="4">
         <v>44679</v>
@@ -2682,10 +2688,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="C14" s="4">
         <v>44743</v>
@@ -2697,10 +2703,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="C15" s="4">
         <v>44748</v>
@@ -2712,10 +2718,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>65</v>
+        <v>11</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="C16" s="4">
         <v>44768</v>
@@ -2727,10 +2733,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="C17" s="4">
         <v>44771</v>
@@ -2742,10 +2748,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>68</v>
+        <v>19</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C18" s="4">
         <v>44786</v>
@@ -2757,10 +2763,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="C19" s="4">
         <v>44794</v>
@@ -2772,10 +2778,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="4">
         <v>44902</v>
@@ -2787,10 +2793,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>72</v>
+        <v>43</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C21" s="4">
         <v>44918</v>
@@ -2802,10 +2808,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>73</v>
+        <v>51</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="4">
         <v>44944</v>
@@ -2835,29 +2841,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="7">
+        <v>79</v>
+      </c>
+      <c r="C2" s="8">
         <v>44749</v>
       </c>
       <c r="D2" s="5">
@@ -2867,12 +2873,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="7">
+        <v>80</v>
+      </c>
+      <c r="C3" s="8">
         <v>44844</v>
       </c>
       <c r="D3" s="5">
@@ -2882,12 +2888,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="7">
+        <v>82</v>
+      </c>
+      <c r="C4" s="8">
         <v>44893</v>
       </c>
       <c r="D4" s="5">
@@ -2897,12 +2903,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="7">
+        <v>83</v>
+      </c>
+      <c r="C5" s="8">
         <v>44895</v>
       </c>
       <c r="D5" s="5">
@@ -2912,12 +2918,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="7">
+        <v>84</v>
+      </c>
+      <c r="C6" s="8">
         <v>44900</v>
       </c>
       <c r="D6" s="5">
@@ -2927,12 +2933,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="7">
+        <v>85</v>
+      </c>
+      <c r="C7" s="8">
         <v>44903</v>
       </c>
       <c r="D7" s="5">
@@ -2942,12 +2948,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="7">
+        <v>86</v>
+      </c>
+      <c r="C8" s="8">
         <v>44916</v>
       </c>
       <c r="D8" s="5">
@@ -2957,12 +2963,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="7">
+        <v>87</v>
+      </c>
+      <c r="C9" s="8">
         <v>44938</v>
       </c>
       <c r="D9" s="5">
@@ -2972,12 +2978,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="7">
+        <v>88</v>
+      </c>
+      <c r="C10" s="8">
         <v>44954</v>
       </c>
       <c r="D10" s="5">
@@ -2987,12 +2993,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="7">
+        <v>89</v>
+      </c>
+      <c r="C11" s="8">
         <v>44973</v>
       </c>
       <c r="D11" s="5">
@@ -3002,12 +3008,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="7">
+        <v>90</v>
+      </c>
+      <c r="C12" s="8">
         <v>44978</v>
       </c>
       <c r="D12" s="5">
@@ -3017,12 +3023,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="7">
+        <v>91</v>
+      </c>
+      <c r="C13" s="8">
         <v>45001</v>
       </c>
       <c r="D13" s="5">
@@ -3032,12 +3038,12 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="7">
+        <v>92</v>
+      </c>
+      <c r="C14" s="8">
         <v>45007</v>
       </c>
       <c r="D14" s="5">
@@ -3047,12 +3053,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="7">
+        <v>93</v>
+      </c>
+      <c r="C15" s="8">
         <v>45007</v>
       </c>
       <c r="D15" s="5">
@@ -3062,12 +3068,12 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="7">
+        <v>94</v>
+      </c>
+      <c r="C16" s="8">
         <v>45044</v>
       </c>
       <c r="D16" s="5">
@@ -3077,12 +3083,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="7">
+        <v>95</v>
+      </c>
+      <c r="C17" s="8">
         <v>45050</v>
       </c>
       <c r="D17" s="5">
@@ -3092,12 +3098,12 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="7">
+        <v>97</v>
+      </c>
+      <c r="C18" s="8">
         <v>45054</v>
       </c>
       <c r="D18" s="5">
@@ -3107,12 +3113,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="7">
+        <v>98</v>
+      </c>
+      <c r="C19" s="8">
         <v>45076</v>
       </c>
       <c r="D19" s="5">
@@ -3122,12 +3128,12 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="7">
+        <v>99</v>
+      </c>
+      <c r="C20" s="8">
         <v>45092</v>
       </c>
       <c r="D20" s="5">
@@ -3137,12 +3143,12 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="7">
+        <v>100</v>
+      </c>
+      <c r="C21" s="8">
         <v>45125</v>
       </c>
       <c r="D21" s="5">
@@ -3152,12 +3158,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="7">
+        <v>102</v>
+      </c>
+      <c r="C22" s="8">
         <v>45133</v>
       </c>
       <c r="D22" s="5">
@@ -3167,12 +3173,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="7">
+        <v>103</v>
+      </c>
+      <c r="C23" s="8">
         <v>45141</v>
       </c>
       <c r="D23" s="5">
@@ -3182,12 +3188,12 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="7">
+        <v>104</v>
+      </c>
+      <c r="C24" s="8">
         <v>45145</v>
       </c>
       <c r="D24" s="5">
@@ -3197,12 +3203,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="7">
+        <v>105</v>
+      </c>
+      <c r="C25" s="8">
         <v>45224</v>
       </c>
       <c r="D25" s="5">
@@ -3212,12 +3218,12 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="7">
+        <v>106</v>
+      </c>
+      <c r="C26" s="8">
         <v>45231</v>
       </c>
       <c r="D26" s="5">
@@ -3245,29 +3251,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="7">
+        <v>107</v>
+      </c>
+      <c r="C2" s="8">
         <v>44742</v>
       </c>
       <c r="D2" s="5">
@@ -3277,12 +3283,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="7">
+        <v>108</v>
+      </c>
+      <c r="C3" s="8">
         <v>44836</v>
       </c>
       <c r="D3" s="5">
@@ -3292,12 +3298,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="7">
+        <v>109</v>
+      </c>
+      <c r="C4" s="8">
         <v>44848</v>
       </c>
       <c r="D4" s="5">
@@ -3307,12 +3313,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="7">
+        <v>110</v>
+      </c>
+      <c r="C5" s="8">
         <v>44858</v>
       </c>
       <c r="D5" s="5">
@@ -3322,12 +3328,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="7">
+        <v>111</v>
+      </c>
+      <c r="C6" s="8">
         <v>44862</v>
       </c>
       <c r="D6" s="5">
@@ -3337,12 +3343,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="7">
+        <v>112</v>
+      </c>
+      <c r="C7" s="8">
         <v>44862</v>
       </c>
       <c r="D7" s="5">
@@ -3352,12 +3358,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="7">
+        <v>113</v>
+      </c>
+      <c r="C8" s="8">
         <v>44866</v>
       </c>
       <c r="D8" s="5">
@@ -3367,12 +3373,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="7">
+        <v>114</v>
+      </c>
+      <c r="C9" s="8">
         <v>44869</v>
       </c>
       <c r="D9" s="5">
@@ -3382,12 +3388,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="7">
+        <v>115</v>
+      </c>
+      <c r="C10" s="8">
         <v>44924</v>
       </c>
       <c r="D10" s="5">
@@ -3397,12 +3403,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="7">
+        <v>116</v>
+      </c>
+      <c r="C11" s="8">
         <v>44930</v>
       </c>
       <c r="D11" s="5">
@@ -3412,12 +3418,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="7">
+        <v>117</v>
+      </c>
+      <c r="C12" s="8">
         <v>44946</v>
       </c>
       <c r="D12" s="5">
@@ -3427,12 +3433,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="7">
+        <v>118</v>
+      </c>
+      <c r="C13" s="8">
         <v>44965</v>
       </c>
       <c r="D13" s="5">
@@ -3442,12 +3448,12 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="7">
+        <v>119</v>
+      </c>
+      <c r="C14" s="8">
         <v>44965</v>
       </c>
       <c r="D14" s="5">
@@ -3457,12 +3463,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="7">
+        <v>120</v>
+      </c>
+      <c r="C15" s="8">
         <v>44984</v>
       </c>
       <c r="D15" s="5">
@@ -3472,12 +3478,12 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="7">
+        <v>121</v>
+      </c>
+      <c r="C16" s="8">
         <v>45008</v>
       </c>
       <c r="D16" s="5">
@@ -3487,12 +3493,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="7">
+        <v>122</v>
+      </c>
+      <c r="C17" s="8">
         <v>45072</v>
       </c>
       <c r="D17" s="5">
@@ -3502,12 +3508,12 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="7">
+        <v>123</v>
+      </c>
+      <c r="C18" s="8">
         <v>45093</v>
       </c>
       <c r="D18" s="5">
@@ -3517,12 +3523,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="7">
+        <v>124</v>
+      </c>
+      <c r="C19" s="8">
         <v>45106</v>
       </c>
       <c r="D19" s="5">
@@ -3532,12 +3538,12 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="7">
+        <v>125</v>
+      </c>
+      <c r="C20" s="8">
         <v>45107</v>
       </c>
       <c r="D20" s="5">
@@ -3547,12 +3553,12 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="7">
+        <v>126</v>
+      </c>
+      <c r="C21" s="8">
         <v>45133</v>
       </c>
       <c r="D21" s="5">
@@ -3562,12 +3568,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="7">
+        <v>127</v>
+      </c>
+      <c r="C22" s="8">
         <v>45147</v>
       </c>
       <c r="D22" s="5">
@@ -3577,12 +3583,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="7">
+        <v>129</v>
+      </c>
+      <c r="C23" s="8">
         <v>45152</v>
       </c>
       <c r="D23" s="5">
@@ -3592,12 +3598,12 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="7">
+        <v>130</v>
+      </c>
+      <c r="C24" s="8">
         <v>45154</v>
       </c>
       <c r="D24" s="5">
@@ -3607,12 +3613,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="7">
+        <v>131</v>
+      </c>
+      <c r="C25" s="8">
         <v>45155</v>
       </c>
       <c r="D25" s="5">
@@ -3622,12 +3628,12 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="7">
+        <v>132</v>
+      </c>
+      <c r="C26" s="8">
         <v>45320</v>
       </c>
       <c r="D26" s="5">
@@ -3655,29 +3661,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="7">
+        <v>159</v>
+      </c>
+      <c r="C2" s="8">
         <v>44579</v>
       </c>
       <c r="D2" s="5">
@@ -3687,12 +3693,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="7">
+        <v>160</v>
+      </c>
+      <c r="C3" s="8">
         <v>44624</v>
       </c>
       <c r="D3" s="5">
@@ -3702,12 +3708,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="7">
+        <v>161</v>
+      </c>
+      <c r="C4" s="8">
         <v>44704</v>
       </c>
       <c r="D4" s="5">
@@ -3717,12 +3723,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C5" s="7">
+        <v>162</v>
+      </c>
+      <c r="C5" s="8">
         <v>44704</v>
       </c>
       <c r="D5" s="5">
@@ -3732,12 +3738,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="7">
+        <v>163</v>
+      </c>
+      <c r="C6" s="8">
         <v>44718</v>
       </c>
       <c r="D6" s="5">
@@ -3747,12 +3753,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="7">
+        <v>164</v>
+      </c>
+      <c r="C7" s="8">
         <v>44764</v>
       </c>
       <c r="D7" s="5">
@@ -3762,12 +3768,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="7">
+        <v>165</v>
+      </c>
+      <c r="C8" s="8">
         <v>44842</v>
       </c>
       <c r="D8" s="5">
@@ -3777,12 +3783,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="7">
+        <v>166</v>
+      </c>
+      <c r="C9" s="8">
         <v>44883</v>
       </c>
       <c r="D9" s="5">
@@ -3792,12 +3798,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="7">
+        <v>167</v>
+      </c>
+      <c r="C10" s="8">
         <v>44954</v>
       </c>
       <c r="D10" s="5">
@@ -3807,12 +3813,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="7">
+        <v>168</v>
+      </c>
+      <c r="C11" s="8">
         <v>45037</v>
       </c>
       <c r="D11" s="5">
@@ -3840,29 +3846,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="7">
+        <v>133</v>
+      </c>
+      <c r="C2" s="8">
         <v>44722</v>
       </c>
       <c r="D2" s="5">
@@ -3872,12 +3878,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="7">
+        <v>134</v>
+      </c>
+      <c r="C3" s="8">
         <v>44722</v>
       </c>
       <c r="D3" s="5">
@@ -3887,12 +3893,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="7">
+        <v>135</v>
+      </c>
+      <c r="C4" s="8">
         <v>44771</v>
       </c>
       <c r="D4" s="5">
@@ -3902,12 +3908,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="7">
+        <v>136</v>
+      </c>
+      <c r="C5" s="8">
         <v>44833</v>
       </c>
       <c r="D5" s="5">
@@ -3917,12 +3923,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="7">
+        <v>137</v>
+      </c>
+      <c r="C6" s="8">
         <v>44853</v>
       </c>
       <c r="D6" s="5">
@@ -3932,12 +3938,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="7">
+        <v>138</v>
+      </c>
+      <c r="C7" s="8">
         <v>44876</v>
       </c>
       <c r="D7" s="5">
@@ -3947,12 +3953,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="7">
+        <v>139</v>
+      </c>
+      <c r="C8" s="8">
         <v>44900</v>
       </c>
       <c r="D8" s="5">
@@ -3962,12 +3968,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="7">
+        <v>140</v>
+      </c>
+      <c r="C9" s="8">
         <v>44902</v>
       </c>
       <c r="D9" s="5">
@@ -3977,12 +3983,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="7">
+        <v>141</v>
+      </c>
+      <c r="C10" s="8">
         <v>44907</v>
       </c>
       <c r="D10" s="5">
@@ -3992,12 +3998,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="7">
+        <v>142</v>
+      </c>
+      <c r="C11" s="8">
         <v>44935</v>
       </c>
       <c r="D11" s="5">
@@ -4007,12 +4013,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="7">
+        <v>143</v>
+      </c>
+      <c r="C12" s="8">
         <v>44936</v>
       </c>
       <c r="D12" s="5">
@@ -4022,12 +4028,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="7">
+        <v>144</v>
+      </c>
+      <c r="C13" s="8">
         <v>44944</v>
       </c>
       <c r="D13" s="5">
@@ -4037,12 +4043,12 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="7">
+        <v>145</v>
+      </c>
+      <c r="C14" s="8">
         <v>44959</v>
       </c>
       <c r="D14" s="5">
@@ -4052,12 +4058,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="7">
+        <v>146</v>
+      </c>
+      <c r="C15" s="8">
         <v>44979</v>
       </c>
       <c r="D15" s="5">
@@ -4067,12 +4073,12 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C16" s="7">
+        <v>147</v>
+      </c>
+      <c r="C16" s="8">
         <v>44981</v>
       </c>
       <c r="D16" s="5">
@@ -4082,12 +4088,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="7">
+        <v>148</v>
+      </c>
+      <c r="C17" s="8">
         <v>45007</v>
       </c>
       <c r="D17" s="5">
@@ -4097,12 +4103,12 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="7">
+        <v>149</v>
+      </c>
+      <c r="C18" s="8">
         <v>45034</v>
       </c>
       <c r="D18" s="5">
@@ -4112,12 +4118,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="7">
+        <v>150</v>
+      </c>
+      <c r="C19" s="8">
         <v>45072</v>
       </c>
       <c r="D19" s="5">
@@ -4127,12 +4133,12 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="7">
+        <v>151</v>
+      </c>
+      <c r="C20" s="8">
         <v>45076</v>
       </c>
       <c r="D20" s="5">
@@ -4142,12 +4148,12 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C21" s="7">
+        <v>152</v>
+      </c>
+      <c r="C21" s="8">
         <v>45117</v>
       </c>
       <c r="D21" s="5">
@@ -4157,12 +4163,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="7">
+        <v>153</v>
+      </c>
+      <c r="C22" s="8">
         <v>45126</v>
       </c>
       <c r="D22" s="5">
@@ -4172,12 +4178,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="7">
+        <v>154</v>
+      </c>
+      <c r="C23" s="8">
         <v>45156</v>
       </c>
       <c r="D23" s="5">
@@ -4187,12 +4193,12 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="7">
+        <v>155</v>
+      </c>
+      <c r="C24" s="8">
         <v>45166</v>
       </c>
       <c r="D24" s="5">
@@ -4202,12 +4208,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="7">
+        <v>156</v>
+      </c>
+      <c r="C25" s="8">
         <v>45189</v>
       </c>
       <c r="D25" s="5">
@@ -4217,12 +4223,12 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="7">
+        <v>157</v>
+      </c>
+      <c r="C26" s="8">
         <v>45219</v>
       </c>
       <c r="D26" s="5">
@@ -4232,12 +4238,12 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="7">
+        <v>158</v>
+      </c>
+      <c r="C27" s="8">
         <v>45220</v>
       </c>
       <c r="D27" s="5">
@@ -4265,29 +4271,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="8">
+        <v>169</v>
+      </c>
+      <c r="C2" s="10">
         <v>44229</v>
       </c>
       <c r="D2" s="5">
@@ -4297,12 +4303,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="8">
+        <v>170</v>
+      </c>
+      <c r="C3" s="10">
         <v>44315</v>
       </c>
       <c r="D3" s="5">
@@ -4312,12 +4318,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="8">
+        <v>171</v>
+      </c>
+      <c r="C4" s="10">
         <v>44385</v>
       </c>
       <c r="D4" s="5">
@@ -4327,12 +4333,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="8">
+        <v>172</v>
+      </c>
+      <c r="C5" s="10">
         <v>44420</v>
       </c>
       <c r="D5" s="5">
@@ -4342,12 +4348,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="8">
+        <v>173</v>
+      </c>
+      <c r="C6" s="10">
         <v>44420</v>
       </c>
       <c r="D6" s="5">
@@ -4357,12 +4363,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="8">
+        <v>174</v>
+      </c>
+      <c r="C7" s="10">
         <v>44440</v>
       </c>
       <c r="D7" s="5">
@@ -4372,12 +4378,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="8">
+        <v>175</v>
+      </c>
+      <c r="C8" s="10">
         <v>44451</v>
       </c>
       <c r="D8" s="5">
@@ -4387,12 +4393,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="8">
+        <v>176</v>
+      </c>
+      <c r="C9" s="10">
         <v>44453</v>
       </c>
       <c r="D9" s="5">
@@ -4402,12 +4408,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="8">
+        <v>177</v>
+      </c>
+      <c r="C10" s="10">
         <v>44456</v>
       </c>
       <c r="D10" s="5">
@@ -4417,12 +4423,12 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="8">
+        <v>178</v>
+      </c>
+      <c r="C11" s="10">
         <v>44456</v>
       </c>
       <c r="D11" s="5">
@@ -4432,12 +4438,12 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="8">
+        <v>179</v>
+      </c>
+      <c r="C12" s="10">
         <v>44468</v>
       </c>
       <c r="D12" s="5">
@@ -4447,12 +4453,12 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" s="8">
+        <v>194</v>
+      </c>
+      <c r="C13" s="10">
         <v>44480</v>
       </c>
       <c r="D13" s="5">
@@ -4462,12 +4468,12 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="8">
+        <v>180</v>
+      </c>
+      <c r="C14" s="10">
         <v>44486</v>
       </c>
       <c r="D14" s="5">
@@ -4477,12 +4483,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="9">
+        <v>181</v>
+      </c>
+      <c r="C15" s="11">
         <v>44516</v>
       </c>
       <c r="D15" s="5">
@@ -4492,12 +4498,12 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="8">
+        <v>182</v>
+      </c>
+      <c r="C16" s="10">
         <v>44516</v>
       </c>
       <c r="D16" s="5">
@@ -4507,12 +4513,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="8">
+        <v>183</v>
+      </c>
+      <c r="C17" s="10">
         <v>44533</v>
       </c>
       <c r="D17" s="5">
@@ -4522,12 +4528,12 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="8">
+        <v>184</v>
+      </c>
+      <c r="C18" s="10">
         <v>44540</v>
       </c>
       <c r="D18" s="5">
@@ -4537,12 +4543,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="8">
+        <v>185</v>
+      </c>
+      <c r="C19" s="10">
         <v>44550</v>
       </c>
       <c r="D19" s="5">
@@ -4552,12 +4558,12 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="8">
+        <v>186</v>
+      </c>
+      <c r="C20" s="10">
         <v>44561</v>
       </c>
       <c r="D20" s="5">
@@ -4567,12 +4573,12 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="8">
+        <v>187</v>
+      </c>
+      <c r="C21" s="10">
         <v>44561</v>
       </c>
       <c r="D21" s="5">
@@ -4582,12 +4588,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="8">
+        <v>188</v>
+      </c>
+      <c r="C22" s="10">
         <v>44567</v>
       </c>
       <c r="D22" s="5">
@@ -4597,12 +4603,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="8">
+        <v>189</v>
+      </c>
+      <c r="C23" s="10">
         <v>44585</v>
       </c>
       <c r="D23" s="5">
@@ -4612,12 +4618,12 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="8">
+        <v>190</v>
+      </c>
+      <c r="C24" s="10">
         <v>44629</v>
       </c>
       <c r="D24" s="5">
@@ -4627,12 +4633,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C25" s="8">
+        <v>191</v>
+      </c>
+      <c r="C25" s="10">
         <v>44645</v>
       </c>
       <c r="D25" s="5">
@@ -4642,12 +4648,12 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="9">
+        <v>192</v>
+      </c>
+      <c r="C26" s="11">
         <v>44672</v>
       </c>
       <c r="D26" s="5">
@@ -4657,12 +4663,12 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C27" s="8">
+        <v>193</v>
+      </c>
+      <c r="C27" s="10">
         <v>44884</v>
       </c>
       <c r="D27" s="5">
@@ -4690,29 +4696,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" s="7">
+        <v>195</v>
+      </c>
+      <c r="C2" s="8">
         <v>44591</v>
       </c>
       <c r="D2" s="5">
@@ -4722,12 +4728,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="7">
+        <v>196</v>
+      </c>
+      <c r="C3" s="8">
         <v>44767</v>
       </c>
       <c r="D3" s="5">
@@ -4737,12 +4743,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="7">
+        <v>197</v>
+      </c>
+      <c r="C4" s="8">
         <v>44823</v>
       </c>
       <c r="D4" s="5">
@@ -4752,12 +4758,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="7">
+        <v>198</v>
+      </c>
+      <c r="C5" s="8">
         <v>44825</v>
       </c>
       <c r="D5" s="5">
@@ -4767,12 +4773,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="7">
+        <v>199</v>
+      </c>
+      <c r="C6" s="8">
         <v>44900</v>
       </c>
       <c r="D6" s="5">
@@ -4782,12 +4788,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="7">
+        <v>200</v>
+      </c>
+      <c r="C7" s="8">
         <v>45062</v>
       </c>
       <c r="D7" s="5">
@@ -4797,12 +4803,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="7">
+        <v>250</v>
+      </c>
+      <c r="C8" s="8">
         <v>45147</v>
       </c>
       <c r="D8" s="5">
@@ -4830,29 +4836,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="7">
+        <v>5</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="8">
         <v>44875</v>
       </c>
       <c r="D2" s="5">
@@ -4862,12 +4868,12 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="7">
+        <v>202</v>
+      </c>
+      <c r="C3" s="8">
         <v>44925</v>
       </c>
       <c r="D3" s="5">
@@ -4877,12 +4883,12 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="7">
+        <v>203</v>
+      </c>
+      <c r="C4" s="8">
         <v>44955</v>
       </c>
       <c r="D4" s="5">
@@ -4892,12 +4898,12 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="7">
+        <v>204</v>
+      </c>
+      <c r="C5" s="8">
         <v>45093</v>
       </c>
       <c r="D5" s="5">
@@ -4907,12 +4913,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" s="7">
+        <v>205</v>
+      </c>
+      <c r="C6" s="8">
         <v>45294</v>
       </c>
       <c r="D6" s="5">
@@ -4922,12 +4928,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="7">
+        <v>206</v>
+      </c>
+      <c r="C7" s="8">
         <v>45313</v>
       </c>
       <c r="D7" s="5">
@@ -4937,12 +4943,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="7">
+        <v>207</v>
+      </c>
+      <c r="C8" s="8">
         <v>45363</v>
       </c>
       <c r="D8" s="5">
@@ -4952,12 +4958,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="7">
+        <v>208</v>
+      </c>
+      <c r="C9" s="8">
         <v>45422</v>
       </c>
       <c r="D9" s="5">
